--- a/Testing_Websites/Testing Websites.xlsx
+++ b/Testing_Websites/Testing Websites.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>TESTING WEBSITES</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>https://single-page-vuln-search.vercel.app/</t>
+  </si>
+  <si>
+    <t>Single Page Vuln Blog</t>
+  </si>
+  <si>
+    <t>https://single-page-vuln-blog.vercel.app/</t>
   </si>
   <si>
     <t>Multiple Page</t>
@@ -504,12 +510,16 @@
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" ht="36.75" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -535,19 +545,19 @@
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -574,16 +584,16 @@
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="B7" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -612,10 +622,10 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -29439,20 +29449,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:A8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C4"/>
     <hyperlink r:id="rId2" ref="E4"/>
-    <hyperlink r:id="rId3" ref="C6"/>
-    <hyperlink r:id="rId4" ref="E6"/>
-    <hyperlink r:id="rId5" ref="C7"/>
-    <hyperlink r:id="rId6" ref="E7"/>
-    <hyperlink r:id="rId7" ref="E8"/>
+    <hyperlink r:id="rId3" ref="E5"/>
+    <hyperlink r:id="rId4" ref="C6"/>
+    <hyperlink r:id="rId5" ref="E6"/>
+    <hyperlink r:id="rId6" ref="C7"/>
+    <hyperlink r:id="rId7" ref="E7"/>
+    <hyperlink r:id="rId8" ref="E8"/>
   </hyperlinks>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>